--- a/public/templates/product.xlsx
+++ b/public/templates/product.xlsx
@@ -55,7 +55,7 @@
       <color rgb="FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -78,6 +78,24 @@
         <bgColor/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -128,7 +146,7 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -137,6 +155,11 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -472,18 +495,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:I3"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
     <col min="2" max="2" width="23.83203125" customWidth="1"/>
     <col min="3" max="3" width="14.83203125" customWidth="1"/>
     <col min="4" max="4" width="9.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="5" max="5" width="20.83203125" customWidth="1"/>
+    <col min="6" max="6" width="19.83203125" customWidth="1"/>
     <col min="7" max="7" width="19.83203125" customWidth="1"/>
-    <col min="8" max="8" width="19.83203125" customWidth="1"/>
-    <col min="9" max="9" width="35.83203125" customWidth="1"/>
-    <col min="10" max="10" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="35.83203125" customWidth="1"/>
+    <col min="9" max="9" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -500,53 +522,47 @@
         <v>Uom</v>
       </c>
       <c r="E1" s="4" t="str">
-        <v>Supplier</v>
+        <v>Purchase Price</v>
       </c>
       <c r="F1" s="4" t="str">
-        <v>Purchase Price</v>
+        <v>Selling Price</v>
       </c>
       <c r="G1" s="4" t="str">
-        <v>Selling Price</v>
+        <v>Barcode</v>
       </c>
       <c r="H1" s="4" t="str">
-        <v>Barcode</v>
+        <v>Description</v>
       </c>
       <c r="I1" s="4" t="str">
-        <v>Description</v>
-      </c>
-      <c r="J1" s="4" t="str">
         <v>Is Active</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="5" t="str">
         <v>PRD-001</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="6" t="str">
         <v>KOPI ARABIKA 250G</v>
       </c>
-      <c r="C2" s="2" t="str">
+      <c r="C2" s="6" t="str">
         <v>BVG</v>
       </c>
-      <c r="D2" s="2" t="str">
+      <c r="D2" s="6" t="str">
         <v>PCS</v>
       </c>
-      <c r="E2" s="2" t="str">
-        <v>SUP-001</v>
-      </c>
-      <c r="F2" s="5">
+      <c r="E2" s="7">
         <v>35000</v>
       </c>
-      <c r="G2" s="5">
+      <c r="F2" s="7">
         <v>52000</v>
       </c>
-      <c r="H2" s="2" t="str">
+      <c r="G2" s="6" t="str">
         <v>8991234567890</v>
       </c>
-      <c r="I2" s="2" t="str">
+      <c r="H2" s="6" t="str">
         <v>Kopi arabika kemasan 250 gram</v>
       </c>
-      <c r="J2" s="2" t="b">
+      <c r="I2" s="6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -563,28 +579,25 @@
       <c r="D3" s="2" t="str">
         <v>PCS</v>
       </c>
-      <c r="E3" s="2" t="str">
-        <v>SUP-002</v>
-      </c>
-      <c r="F3" s="5">
+      <c r="E3" s="8">
         <v>18000</v>
       </c>
-      <c r="G3" s="5">
+      <c r="F3" s="8">
         <v>27500</v>
       </c>
+      <c r="G3" s="2" t="str">
+        <v>8991234567891</v>
+      </c>
       <c r="H3" s="2" t="str">
-        <v>8991234567891</v>
-      </c>
-      <c r="I3" s="2" t="str">
         <v>Gula aren organik 500 gram</v>
       </c>
-      <c r="J3" s="2" t="b">
+      <c r="I3" s="2" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
   </ignoredErrors>
 </worksheet>
 </file>